--- a/data/trans_orig/P34B04-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P34B04-Estudios-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de días a la semana que la población realiza un entrenamiento físico deportivo, como fútbol, baloncesto, ciclismo, natación de competición, judo, kárate o similares</t>
+          <t>Número medio de días a la semana que, durante más de 30 minutos, la población realiza un entrenamiento físico deportivo, como fútbol, baloncesto, ciclismo, natación de competición, judo, kárate o similares (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -682,7 +682,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,2</t>
+          <t>0,08; 0,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -787,12 +787,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,51</t>
+          <t>0,4; 0,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,43</t>
+          <t>0,33; 0,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,13</t>
+          <t>0,06; 0,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,29</t>
+          <t>0,22; 0,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,32</t>
+          <t>0,21; 0,31</t>
         </is>
       </c>
     </row>
@@ -897,27 +897,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,59</t>
+          <t>0,36; 0,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,58</t>
+          <t>0,35; 0,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,76</t>
+          <t>0,49; 0,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,22</t>
+          <t>0,05; 0,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,18</t>
+          <t>0,08; 0,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,36</t>
+          <t>0,24; 0,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,09</t>
+          <t>0,05; 0,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,23</t>
+          <t>0,18; 0,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">

--- a/data/trans_orig/P34B04-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P34B04-Estudios-trans_orig.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,06</t>
         </is>
       </c>
     </row>
@@ -677,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,12</t>
+          <t>0,05; 0,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,2</t>
+          <t>0,07; 0,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,17</t>
+          <t>0,06; 0,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,02</t>
+          <t>0,0; 0,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,09</t>
+          <t>0,04; 0,11</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,28</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 0,51</t>
+          <t>0,4; 0,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,45</t>
+          <t>0,33; 0,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,52</t>
+          <t>0,39; 0,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,12</t>
+          <t>0,07; 0,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,31</t>
+          <t>0,24; 0,33</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,6</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,38</t>
         </is>
       </c>
     </row>
@@ -897,22 +897,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,6</t>
+          <t>0,36; 0,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 0,58</t>
+          <t>0,37; 0,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,75</t>
+          <t>0,51; 0,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,2</t>
+          <t>0,05; 0,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -922,17 +922,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,21</t>
+          <t>0,1; 0,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,37</t>
+          <t>0,22; 0,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,37</t>
+          <t>0,23; 0,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,26</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,47</t>
+          <t>0,38; 0,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,09</t>
+          <t>0,06; 0,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,11</t>
+          <t>0,08; 0,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,28</t>
+          <t>0,23; 0,29</t>
         </is>
       </c>
     </row>
